--- a/existing_customer/files/b2b_agentic_streamlit_demo_data.xlsx
+++ b/existing_customer/files/b2b_agentic_streamlit_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumandeep.a.kaur\Documents\B2B Agentic Screens Demo - Existing Customers\b2b_leadmanagement_apps\existing_customer\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhilasha.anand\b2b_streamlit_apps\acquisition\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D386A898-CEFF-4DD8-831C-775C02AE073C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D2475F-095E-4C4F-ACA2-B701589A69C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="701" xr2:uid="{F9668476-116F-4EE7-B02C-E81D09556175}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="701" xr2:uid="{F9668476-116F-4EE7-B02C-E81D09556175}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer360" sheetId="10" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Customer360!$A$1:$DF$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -122,9 +123,6 @@
     <t>https://www.linkedin.com/company/ironbuild-infrastructure</t>
   </si>
   <si>
-    <t>• Networking &amp; Connectivity: Cisco Catalyst Switches, Cisco Firewalls, WAN routing• Cloud &amp; Infrastructure: AWS EC2, Azure Virtual Machines, backup &amp; recovery• IT Security: Fortinet Firewall, Rapid7 Vulnerability Management• Data &amp; Analytics: Microsoft Power BI• CRM / Enterprise Apps: Salesforce CRM, project management tools</t>
-  </si>
-  <si>
     <t>Tech_Maturity_Tier</t>
   </si>
   <si>
@@ -371,24 +369,6 @@
     <t>Intent_Summary</t>
   </si>
   <si>
-    <t>Networking</t>
-  </si>
-  <si>
-    <t>SD-WAN optimisation, Ethernet networking, bandwidth expansion, network modernisation, site connectivity</t>
-  </si>
-  <si>
-    <t>IoT &amp; Edge</t>
-  </si>
-  <si>
-    <t>IoT networks, asset monitoring, edge connectivity, device management, remote telemetry</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>network security, secure SD-WAN, threat protection, firewall upgrades, perimeter security</t>
-  </si>
-  <si>
     <t>Cisco, Optus</t>
   </si>
   <si>
@@ -434,9 +414,6 @@
     <t>0</t>
   </si>
   <si>
-    <t>• Business Expansion: Secured multiple multi-year civil infrastructure projects across NSW and QLD during FY24–FY25, increasing active construction sites.• Partnerships: Formed regional delivery partnerships to accelerate large-scale project execution.• Financials: Reported ~12% YoY revenue growth driven by sustained public infrastructure investment.</t>
-  </si>
-  <si>
     <t>Company_Annual_SW_Spending_Bucket</t>
   </si>
   <si>
@@ -506,7 +483,31 @@
     <t>Active_Products</t>
   </si>
   <si>
-    <t>https://www.australianconstructionnews.com.au/ironbuild-secures-major-nsw-infrastructure-projects, https://www.infrainsights.com.au/ironbuild-expands-partner-network, https://www.afr.com.au/ironbuild-reports-strong-fy24-revenue-growth</t>
+    <t xml:space="preserve">• Networking &amp; Connectivity: Cisco Catalyst Switches, Cisco Firewalls, WAN routing• Cloud &amp; Infrastructure: AWS EC2, Azure Virtual Machines, backup &amp; recovery• IT Security: Fortinet Firewall, Rapid7 Vulnerability Management• Data &amp; Analytics: Microsoft Power BI• CRM / Enterprise Apps: Salesforce CRM, project management tools• ERP: SAP S/4HANA </t>
+  </si>
+  <si>
+    <t>Network Infrastructure</t>
+  </si>
+  <si>
+    <t>Bandwidth expansion, Ethernet networking, SD-WAN optimization</t>
+  </si>
+  <si>
+    <t>IoT &amp; Asset Management</t>
+  </si>
+  <si>
+    <t>Equipment monitoring systems, Heavy equipment fleet management, Construction IoT telemetry, Asset tracking systems, Fleet telematics</t>
+  </si>
+  <si>
+    <t>AI &amp; Automation</t>
+  </si>
+  <si>
+    <t>Construction AI solutions, Site safety automation, AI workforce scheduling, Computer vision construction</t>
+  </si>
+  <si>
+    <t>• Business Expansion: Secured multiple multi-year civil infrastructure projects across NSW and QLD during FY24–FY25, increasing active construction sites with the equipment asset base scaling in line with site growth.• Partnerships: Formed regional delivery partnerships to accelerate large-scale project execution.• Hiring: Actively hiring across site operations.• Financials: Reported ~12% YoY revenue growth driven by sustained public infrastructure investment.• Digital Transformation: Announced enterprise-wide digital transformation initiative to modernize construction operations.</t>
+  </si>
+  <si>
+    <t>https://www.australianconstructionnews.com.au/ironbuild-secures-major-nsw-infrastructure-projects, https://www.infrainsights.com.au/ironbuild-expands-partner-network, https://www.constructioncareers.com.au/ironbuild-ramps-up-site-hiring, https://www.afr.com.au/ironbuild-reports-strong-fy24-revenue-growth, https://www.infrastructuretechnews.com.au/ironbuild-launches-digital-transformation</t>
   </si>
 </sst>
 </file>
@@ -989,20 +990,20 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:DF2"/>
-  <sheetFormatPr defaultColWidth="23" defaultRowHeight="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23" defaultRowHeight="50.1" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.7109375" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" style="2" customWidth="1"/>
-    <col min="8" max="93" width="26.7109375" customWidth="1"/>
-    <col min="94" max="99" width="26.7109375" style="3" customWidth="1"/>
-    <col min="100" max="108" width="26.7109375" customWidth="1"/>
-    <col min="109" max="109" width="26.7109375" style="1" customWidth="1"/>
-    <col min="110" max="110" width="26.7109375" customWidth="1"/>
+    <col min="1" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" customWidth="1"/>
+    <col min="7" max="7" width="26.6640625" style="2" customWidth="1"/>
+    <col min="8" max="93" width="26.6640625" customWidth="1"/>
+    <col min="94" max="99" width="26.6640625" style="3" customWidth="1"/>
+    <col min="100" max="108" width="26.6640625" customWidth="1"/>
+    <col min="109" max="109" width="26.6640625" style="1" customWidth="1"/>
+    <col min="110" max="110" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:110" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:110" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1026,7 @@
         <v>7</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>8</v>
@@ -1034,13 +1035,13 @@
         <v>24</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>6</v>
@@ -1058,274 +1059,274 @@
         <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="U1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="V1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AK1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AJ1" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AM1" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="AN1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AP1" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="AP1" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AR1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AR1" s="4" t="s">
+      <c r="AS1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AS1" s="4" t="s">
+      <c r="AT1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AT1" s="4" t="s">
+      <c r="AU1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AV1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="AV1" s="4" t="s">
+      <c r="AW1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AW1" s="4" t="s">
+      <c r="AX1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AX1" s="4" t="s">
+      <c r="AY1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AY1" s="4" t="s">
+      <c r="AZ1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="AZ1" s="4" t="s">
+      <c r="BA1" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="BA1" s="4" t="s">
+      <c r="BB1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="BB1" s="4" t="s">
+      <c r="BC1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="BC1" s="4" t="s">
+      <c r="BD1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BD1" s="4" t="s">
+      <c r="BE1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE1" s="4" t="s">
+      <c r="BF1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="BF1" s="4" t="s">
+      <c r="BG1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="BG1" s="4" t="s">
+      <c r="BH1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="BH1" s="4" t="s">
+      <c r="BI1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="BI1" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="BJ1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="BK1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BK1" s="4" t="s">
+      <c r="BL1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="BL1" s="4" t="s">
+      <c r="BM1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="BM1" s="4" t="s">
+      <c r="BN1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="BN1" s="4" t="s">
+      <c r="BO1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="BP1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="BO1" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="BP1" s="4" t="s">
+      <c r="BQ1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="BQ1" s="4" t="s">
+      <c r="BR1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="BR1" s="4" t="s">
+      <c r="BS1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="BT1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="BU1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="BS1" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="BT1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="BU1" s="4" t="s">
+      <c r="BV1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="BV1" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="BW1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="BX1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="BY1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="BX1" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="BY1" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="BZ1" s="4" t="s">
+      <c r="CA1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CB1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="CB1" s="4" t="s">
+      <c r="CC1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="CC1" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="CD1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="CE1" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="CE1" s="4" t="s">
+      <c r="CF1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="CF1" s="4" t="s">
+      <c r="CG1" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="CG1" s="4" t="s">
+      <c r="CH1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="CH1" s="4" t="s">
+      <c r="CI1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="CI1" s="4" t="s">
+      <c r="CJ1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="CJ1" s="4" t="s">
+      <c r="CK1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="CK1" s="4" t="s">
+      <c r="CL1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="CL1" s="4" t="s">
+      <c r="CM1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="CM1" s="4" t="s">
+      <c r="CN1" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="CN1" s="4" t="s">
+      <c r="CO1" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="CO1" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="CP1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="CQ1" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="CR1" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="CR1" s="16" t="s">
+      <c r="CS1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="CS1" s="16" t="s">
+      <c r="CT1" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="CT1" s="16" t="s">
+      <c r="CU1" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="CU1" s="16" t="s">
-        <v>32</v>
-      </c>
       <c r="CV1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="CW1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="CX1" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="CY1" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="CZ1" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="DA1" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="DB1" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="DC1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="CW1" s="4" t="s">
+      <c r="DD1" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="CX1" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="CY1" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="CZ1" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="DA1" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="DB1" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="DC1" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="DD1" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="DE1" s="4" t="s">
         <v>11</v>
@@ -1334,18 +1335,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:110" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:110" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E2" s="6">
         <v>2008</v>
@@ -1379,13 +1380,13 @@
         <v>26</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="S2" s="9">
         <v>44531</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U2" s="9">
         <v>42522</v>
@@ -1407,7 +1408,7 @@
         <v>0.85</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AB2" s="10"/>
       <c r="AC2" s="10"/>
@@ -1425,13 +1426,13 @@
       </c>
       <c r="AJ2" s="10">
         <f ca="1">IF(AI2="", "",  DATEDIF(TODAY(), AI2, "M") )</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" s="10">
         <v>6</v>
       </c>
       <c r="AL2" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AM2" s="9">
         <v>43252</v>
@@ -1450,7 +1451,7 @@
         <v>180</v>
       </c>
       <c r="AR2" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AS2" s="10"/>
       <c r="AT2" s="10"/>
@@ -1472,16 +1473,16 @@
       <c r="BJ2" s="10"/>
       <c r="BK2" s="10"/>
       <c r="BL2" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="BM2" s="10" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="BN2" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="BO2" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="BP2" s="11">
         <v>0.61</v>
@@ -1502,112 +1503,112 @@
         <v>1</v>
       </c>
       <c r="BV2" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BW2" s="10" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="BX2" s="10" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="BY2" s="10" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="BZ2" s="10" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CA2" s="10" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="CB2" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="CC2" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="CC2" s="10" t="s">
-        <v>97</v>
-      </c>
       <c r="CD2" s="10" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="CE2" s="10">
         <v>85</v>
       </c>
       <c r="CF2" s="10" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="CG2" s="10" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="CH2" s="10">
         <v>72</v>
       </c>
       <c r="CI2" s="10" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="CJ2" s="10" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="CK2" s="10">
         <v>68</v>
       </c>
       <c r="CL2" s="10" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="CM2" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="CN2" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="CO2" s="10" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="CP2" s="6" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="CQ2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="CR2" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CS2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="CT2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="CU2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CU2" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="CV2" s="14" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="CW2" s="14" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="CX2" s="14" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="CY2" s="14" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="CZ2" s="14" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="DA2" s="14" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="DB2" s="14" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="DC2" s="14" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="DD2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="DE2" s="15" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="DF2" s="15" t="s">
         <v>155</v>
